--- a/光伏配储项目/电价数据/2026/汾江站.xlsx
+++ b/光伏配储项目/电价数据/2026/汾江站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51142</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7669600000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5748099999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6083500000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5234099999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.52155</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43758</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45442</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44392</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42364</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42227</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40898</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41386</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41326</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44439</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.24359</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.1331</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10799</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.12475</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.11467</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13798</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.05109</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11556</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.17024</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.12886</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.00015</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09181</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10558</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.03793999999999999</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15428</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21759</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.26079</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.13374</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.25121</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.07892</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00233</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14579</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.24469</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28879</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.25575</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.2192</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.67906</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55967</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.59988</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.41958</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.63885</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.47185</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44815</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42987</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.58396</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.48721</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6516900000000001</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.83577</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.64567</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.66313</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.26567</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43565</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7005</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6049800000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.87497</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.65565</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.66275</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.66144</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.63266</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.48259</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4803</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42566</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71621</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.7413</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.79243</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.51784</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.84749</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53438</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51862</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5051600000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51198</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48869</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40337</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4698</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49963</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.60121</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7367899999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42932</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.43871</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.52907</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.18246</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.42129</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.51322</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.77358</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.27923</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.39633</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.44735</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.82282</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.54438</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.15052</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.53313</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.28213</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.45526</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.6655599999999999</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.80864</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.6576799999999999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.70933</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7902100000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.69376</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.61291</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77798</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.61287</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.46386</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.05711</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.47786</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6633600000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43849</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42511</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33455</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51718</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.54453</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.43607</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40548</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45511</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44936</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.5039</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.22804</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.5280499999999999</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26918</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.48262</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.41381</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.5267000000000001</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49581</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.44024</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.17587</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.29409</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27965</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.40334</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.4401600000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.54304</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.46984</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.47076</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.58302</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.65523</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.77891</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.57492</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.51444</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45517</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5497799999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.43589</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45925</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.48063</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.46648</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.42814</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.45145</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.41063</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41598</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34241</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.41077</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46078</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.23059</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.19151</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.27403</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5421699999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45881</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.11468</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.18003</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.1975</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.24616</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.5528</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07676999999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.13908</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.24793</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.25973</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.22076</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.23936</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20486</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.12131</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.27218</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.6565700000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.47016</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.43507</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30035</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29034</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28981</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27863</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25944</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.05382</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04090999999999999</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.05431</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.05633</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04461</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04265</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04921</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03577</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04693</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04706</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04521</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04646</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04624</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04938</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04313</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04185</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04416</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04553</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04951</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21819</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04147</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04729999999999999</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05529999999999999</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04975</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04721</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00431</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.02369</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.16134</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.06055</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11701</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39211</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46738</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35065</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.68288</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39975</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44524</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42245</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42236</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10257</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04385</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04693</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04522</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04614</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04613</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04614</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04554</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04387</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04565</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09991</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00362</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04452</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04387</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04557</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0432</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04543999999999999</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04562</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04475</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04522</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04357</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04412</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04729999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04904</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04449</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04989</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04725</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04764</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20008</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14297</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26905</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29409</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33552</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31781</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40446</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28134</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29094</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28819</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28107</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27135</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27115</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17253</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15878</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17107</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14782</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15955</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15872</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23634</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21413</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22669</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26889</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28591</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29095</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29096</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28107</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28067</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27227</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42831</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45525</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41833</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15626</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50776</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79092</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6221</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49807</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7811</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9205800000000001</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49469</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91595</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86709</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29909</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89232</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63261</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19188</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87119</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5427999999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33568</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03628</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53554</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7949299999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5296799999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77697</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7806799999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87726</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87593</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49685</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40231</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4047</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45419</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2118</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8790399999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55115</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62663</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53953</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4991</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45646</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42487</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43804</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45021</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42012</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41466</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43362</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45081</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58586</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42721</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59575</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66328</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47602</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5825</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45274</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88197</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63318</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.88298</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.86551</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86656</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44458</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.47368</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40958</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45173</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41451</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35331</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92111</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46551</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41367</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47019</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49916</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16635</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26278</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19904</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.1959</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27881</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28933</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25572</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27989</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43252</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28539</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44779</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5952499999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8901</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.33369</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14029</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6990299999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78955</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64581</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57856</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44924</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50024</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43967</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43695</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41481</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41271</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42306</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.4996</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43392</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42732</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4233</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41275</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42282</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49588</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36279</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29718</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37813</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.27297</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.64025</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.41743</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25053</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.30243</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.69917</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.45211</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.86505</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.44182</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26422</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26399</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.41101</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.58008</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46228</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7545599999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46432</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4367200000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42018</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32357</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42164</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.37121</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.17069</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.17617</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.18306</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.58307</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.51882</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15243</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.16513</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.15262</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.16347</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.16824</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.16249</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.23241</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.13541</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.13768</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.21319</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16259</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16777</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.44324</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.41354</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44849</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44081</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43784</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44275</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38991</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39709</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34847</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5371699999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46732</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41481</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39211</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28199</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27064</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26518</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20274</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24942</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24231</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26903</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.24334</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27412</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24104</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.28601</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28457</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24188</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.43893</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35988</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41544</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41798</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.38408</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.47775</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44229</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.14901</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24969</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.12736</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18308</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.23052</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27232</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43809</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.45164</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42564</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71082</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5343</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26231</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28519</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27821</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.38304</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34942</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42473</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41119</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6515</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.77449</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45753</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3436</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41014</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.45168</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28557</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20151</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26292</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28135</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28033</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22499</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.28152</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.9766</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.8644299999999999</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.86085</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.59601</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.8585499999999999</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.8468300000000001</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43958</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64897</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60505</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5826399999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46541</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.67325</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.46218</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.82559</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.13103</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47676</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42968</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35978</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48964</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53862</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48525</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49464</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39679</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40221</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40917</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40729</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41547</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40954</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4080299999999999</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44914</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44709</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55762</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49896</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44947</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.23784</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45026</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47594</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.42045</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44954</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.49574</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.64367</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.46919</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.41061</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42079</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6557200000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.21594</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42187</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44189</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49397</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.51092</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5104</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.54486</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6952699999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7285</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.67611</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8121499999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.59275</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52354</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.82982</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7699</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6282799999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67464</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45046</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48169</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47661</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46771</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5567000000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.43003</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44132</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43326</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44472</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45344</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39841</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.21137</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04865</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40367</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46181</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11964</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18025</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38107</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.85699</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43065</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42966</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36475</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44429</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22643</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23094</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25078</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.27049</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13927</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25495</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04302</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17191</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18383</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22919</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24973</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23256</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27567</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28436</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34947</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25224</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23786</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16357</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20221</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.25275</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01855</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03048</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04879</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11538</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01856</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03877000000000001</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04882</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.00725</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03309</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.02852</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04647</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.0221</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.01822</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.18704</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04883</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04886</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00173</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.0489</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04867</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04886</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03354</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04881</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04843</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0428</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18431</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.19299</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23316</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28068</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25991</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26695</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.28798</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28678</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28196</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.28026</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.12579</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5657799999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.14739</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28543</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.27664</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.2548</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.26485</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.24126</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.2299</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25847</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.24829</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21301</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.23874</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2408</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26299</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.26311</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24342</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27275</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.27458</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.21951</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.14454</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.63001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.6076900000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.64695</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.58088</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11668</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23599</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17772</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.10815</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.11808</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.06958</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22595</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.1006</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.01717</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.03188</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.09068999999999999</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.16956</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02733</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.10932</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.12022</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.13896</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.02169</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.09156</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.10553</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.10365</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.14246</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.28204</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.47112</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37718</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32307</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5790700000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5597799999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.42554</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.43941</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.39334</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.45664</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.47921</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.4521</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14279</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27029</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28148</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.50318</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3283</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.62436</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.58724</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.51175</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.45162</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26449</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42012</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49683</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.5069900000000001</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.4697</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.4892</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42822</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.6305599999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4347200000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.50019</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38497</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38172</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41582</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45493</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.4045299999999999</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.1209</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36745</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48209</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4044700000000001</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36279</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.42939</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39658</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.47548</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39045</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.40532</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.41113</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.5416599999999999</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.42736</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.5038899999999999</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.46144</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.4406600000000001</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51591</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.58316</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.58631</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.42727</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5286799999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5109900000000001</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5541</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.51985</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.69464</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.86303</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5826699999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39679</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44168</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37228</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25794</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.22994</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27343</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.18438</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.16419</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07659000000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.45402</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.23347</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.04465</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.22289</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01201</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26754</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.17445</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06672</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06032</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.08109000000000001</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17958</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08866</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.18073</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.16343</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.2146</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.25185</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43033</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41707</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42847</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4348399999999999</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35997</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.86602</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.47114</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42592</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.25857</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27989</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.25035</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11453</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.43531</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.46437</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.83253</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.48282</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00398</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01937</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04855</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02023</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.28379</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04835</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.2387</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.27542</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.08502</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1.10397</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.49839</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42447</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.57956</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35944</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.61429</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.45496</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25821</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23053</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14413</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20614</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22975</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23162</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11438</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15047</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.00306</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04727000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04736</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04654999999999999</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04729999999999999</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04682</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04177</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07861</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03001</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06309000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09684999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17055</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19615</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12061</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.2552</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22982</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12417</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05529999999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26258</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14654</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11747</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18526</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23678</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24362</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20354</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24427</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.27425</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4671</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36623</v>
       </c>
     </row>
   </sheetData>
